--- a/Shared/LoadedData.xlsx
+++ b/Shared/LoadedData.xlsx
@@ -629,8 +629,9 @@
   <dimension ref="A3:K46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" bestFit="1" customWidth="1"/>
   </cols>

--- a/Shared/LoadedData.xlsx
+++ b/Shared/LoadedData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="20760" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="34">
   <si>
     <t>Description</t>
   </si>
@@ -120,6 +120,15 @@
   </si>
   <si>
     <t>Slow</t>
+  </si>
+  <si>
+    <t>Default 1</t>
+  </si>
+  <si>
+    <t>Default 2</t>
+  </si>
+  <si>
+    <t>Plague Spreaders 1</t>
   </si>
 </sst>
 </file>
@@ -1335,7 +1344,7 @@
         <v>17</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="H5" s="2">
         <v>3</v>
@@ -1367,7 +1376,7 @@
         <v>20</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="H6" s="2">
         <v>5</v>
@@ -1390,7 +1399,7 @@
         <v>30</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="H7" s="2">
         <v>6</v>
@@ -1517,7 +1526,7 @@
         <v>20</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H5" s="2">
         <v>4</v>

--- a/Shared/LoadedData.xlsx
+++ b/Shared/LoadedData.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="20760" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="35">
   <si>
     <t>Description</t>
   </si>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t>Plague Spreaders 1</t>
+  </si>
+  <si>
+    <t>Support</t>
   </si>
 </sst>
 </file>
@@ -590,6 +593,9 @@
       <c r="H4" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="I4" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="K4" s="1" t="s">
         <v>11</v>
       </c>
@@ -1304,6 +1310,9 @@
       </c>
       <c r="H4" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>11</v>
@@ -1487,6 +1496,9 @@
       <c r="H4" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="I4" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="K4" s="1" t="s">
         <v>11</v>
       </c>

--- a/Shared/LoadedData.xlsx
+++ b/Shared/LoadedData.xlsx
@@ -41,9 +41,6 @@
     <t>Unit Name</t>
   </si>
   <si>
-    <t>Attacks</t>
-  </si>
-  <si>
     <t>Movement</t>
   </si>
   <si>
@@ -132,6 +129,9 @@
   </si>
   <si>
     <t>Support</t>
+  </si>
+  <si>
+    <t>Skills</t>
   </si>
 </sst>
 </file>
@@ -573,49 +573,49 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="S4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="T4" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -653,16 +653,16 @@
   <sheetData>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>0</v>
@@ -671,10 +671,10 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>0</v>
@@ -690,13 +690,13 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J4" s="2">
         <v>1</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1291,57 +1291,57 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="S4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="T4" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:20" s="2" customFormat="true">
       <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="D5" s="2">
         <v>5</v>
@@ -1350,19 +1350,19 @@
         <v>5</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2">
         <v>3</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M5" s="2">
         <v>3</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="6" spans="1:20" s="2" customFormat="true">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" s="2">
         <v>5</v>
@@ -1382,10 +1382,10 @@
         <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2">
         <v>5</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="7" spans="1:20" s="2" customFormat="true">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" s="2">
         <v>5</v>
@@ -1405,10 +1405,10 @@
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H7" s="2">
         <v>6</v>
@@ -1462,7 +1462,7 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -1476,57 +1476,57 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="S4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="T4" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:20" s="2" customFormat="true">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2">
         <v>3</v>
@@ -1535,19 +1535,19 @@
         <v>4</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H5" s="2">
         <v>4</v>
       </c>
       <c r="K5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="M5" s="2">
         <v>4</v>

--- a/Shared/LoadedData.xlsx
+++ b/Shared/LoadedData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="35">
   <si>
     <t>Description</t>
   </si>
@@ -98,12 +98,6 @@
     <t>We're The Rats!</t>
   </si>
   <si>
-    <t>Attack Name</t>
-  </si>
-  <si>
-    <t>Damage</t>
-  </si>
-  <si>
     <t>AP Cost</t>
   </si>
   <si>
@@ -128,10 +122,16 @@
     <t>Plague Spreaders 1</t>
   </si>
   <si>
-    <t>Support</t>
-  </si>
-  <si>
     <t>Skills</t>
+  </si>
+  <si>
+    <t>CombatString</t>
+  </si>
+  <si>
+    <t>Skill Name</t>
+  </si>
+  <si>
+    <t>Universal</t>
   </si>
 </sst>
 </file>
@@ -540,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -551,16 +551,16 @@
     <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="2.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -568,12 +568,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -593,43 +593,40 @@
       <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>33</v>
+      <c r="J4" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="M4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="R4" s="1" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="T4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="17" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="18" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="19" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -641,46 +638,50 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04AD92E6-845E-499F-BA5C-893249301DDF}">
-  <dimension ref="A3:K46"/>
+  <dimension ref="A3:L46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-      <c r="I3" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -689,17 +690,18 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="2"/>
+      <c r="J4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="2">
+      <c r="K4" s="2">
         <v>1</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -711,8 +713,9 @@
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -724,8 +727,9 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -737,8 +741,9 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -750,8 +755,9 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -763,8 +769,9 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -776,8 +783,9 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -789,8 +797,9 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -802,8 +811,9 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -815,8 +825,9 @@
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -828,8 +839,9 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -841,8 +853,9 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -854,8 +867,9 @@
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -867,8 +881,9 @@
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -880,8 +895,9 @@
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L18" s="2"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -893,8 +909,9 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L19" s="2"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -906,8 +923,9 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L20" s="2"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -919,8 +937,9 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L21" s="2"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -932,8 +951,9 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L22" s="2"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -945,8 +965,9 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L23" s="2"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -958,8 +979,9 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L24" s="2"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -971,8 +993,9 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L25" s="2"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -984,8 +1007,9 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L26" s="2"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -997,8 +1021,9 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L27" s="2"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -1010,8 +1035,9 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L28" s="2"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -1023,8 +1049,9 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L29" s="2"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1036,8 +1063,9 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L30" s="2"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -1049,8 +1077,9 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L31" s="2"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -1062,8 +1091,9 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L32" s="2"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -1075,8 +1105,9 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L33" s="2"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -1088,8 +1119,9 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L34" s="2"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -1101,8 +1133,9 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L35" s="2"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -1114,8 +1147,9 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L36" s="2"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -1127,8 +1161,9 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L37" s="2"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -1140,8 +1175,9 @@
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -1153,8 +1189,9 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L39" s="2"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -1166,8 +1203,9 @@
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L40" s="2"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -1179,8 +1217,9 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L41" s="2"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -1192,8 +1231,9 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L42" s="2"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -1205,8 +1245,9 @@
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L43" s="2"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -1218,8 +1259,9 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L44" s="2"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -1231,8 +1273,9 @@
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L45" s="2"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -1244,6 +1287,7 @@
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1291,7 +1335,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -1310,9 +1354,6 @@
       </c>
       <c r="H4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>10</v>
@@ -1353,7 +1394,7 @@
         <v>16</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H5" s="2">
         <v>3</v>
@@ -1385,7 +1426,7 @@
         <v>19</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H6" s="2">
         <v>5</v>
@@ -1393,7 +1434,7 @@
     </row>
     <row r="7" spans="1:20" s="2" customFormat="true">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>15</v>
@@ -1405,10 +1446,10 @@
         <v>5</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="H7" s="2">
         <v>6</v>
@@ -1476,7 +1517,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -1495,9 +1536,6 @@
       </c>
       <c r="H4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>10</v>
@@ -1538,7 +1576,7 @@
         <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2">
         <v>4</v>

--- a/Shared/LoadedData.xlsx
+++ b/Shared/LoadedData.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3"/>
+    <workbookView xWindow="-29490" yWindow="2940" windowWidth="28800" windowHeight="15345" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="40">
   <si>
     <t>Description</t>
   </si>
@@ -132,6 +132,21 @@
   </si>
   <si>
     <t>Universal</t>
+  </si>
+  <si>
+    <t>Basic Attack</t>
+  </si>
+  <si>
+    <t>D(2)</t>
+  </si>
+  <si>
+    <t>Basic Strike</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>Cooldown</t>
   </si>
 </sst>
 </file>
@@ -638,18 +653,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04AD92E6-845E-499F-BA5C-893249301DDF}">
-  <dimension ref="A3:L46"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A3:M46"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" width="12.28515625"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" width="13.140625"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" width="11.140625"/>
+    <col bestFit="true" customWidth="true" max="8" min="8" width="10"/>
+    <col bestFit="true" customWidth="true" max="11" min="11" width="18"/>
+    <col bestFit="true" customWidth="true" max="12" min="12" width="17.7109375"/>
+    <col bestFit="true" customWidth="true" max="13" min="13" width="18"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>33</v>
       </c>
@@ -668,40 +684,62 @@
       <c r="F3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+      <c r="G3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="1"/>
+      <c r="K3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+    <row r="4" spans="1:13">
+      <c r="A4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
       <c r="I4" s="2"/>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="2"/>
+      <c r="K4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="2">
+      <c r="L4" s="2">
         <v>1</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -714,8 +752,9 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M5" s="2"/>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -728,8 +767,9 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -742,8 +782,9 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -756,8 +797,9 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M8" s="2"/>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -770,8 +812,9 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -784,8 +827,9 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M10" s="2"/>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -798,8 +842,9 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M11" s="2"/>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -812,8 +857,9 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M12" s="2"/>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -826,8 +872,9 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M13" s="2"/>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -840,8 +887,9 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M14" s="2"/>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -854,8 +902,9 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M15" s="2"/>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -868,8 +917,9 @@
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -882,8 +932,9 @@
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -896,8 +947,9 @@
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M18" s="2"/>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -910,8 +962,9 @@
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M19" s="2"/>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -924,8 +977,9 @@
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M20" s="2"/>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -938,8 +992,9 @@
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M21" s="2"/>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -952,8 +1007,9 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M22" s="2"/>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -966,8 +1022,9 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M23" s="2"/>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -980,8 +1037,9 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M24" s="2"/>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -994,8 +1052,9 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M25" s="2"/>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -1008,8 +1067,9 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M26" s="2"/>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1022,8 +1082,9 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M27" s="2"/>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -1036,8 +1097,9 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M28" s="2"/>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -1050,8 +1112,9 @@
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M29" s="2"/>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1064,8 +1127,9 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M30" s="2"/>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -1078,8 +1142,9 @@
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M31" s="2"/>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -1092,8 +1157,9 @@
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M32" s="2"/>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -1106,8 +1172,9 @@
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M33" s="2"/>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -1120,8 +1187,9 @@
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M34" s="2"/>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -1134,8 +1202,9 @@
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M35" s="2"/>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -1148,8 +1217,9 @@
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M36" s="2"/>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -1162,8 +1232,9 @@
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M37" s="2"/>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -1176,8 +1247,9 @@
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -1190,8 +1262,9 @@
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M39" s="2"/>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -1204,8 +1277,9 @@
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M40" s="2"/>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -1218,8 +1292,9 @@
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M41" s="2"/>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -1232,8 +1307,9 @@
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M42" s="2"/>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -1246,8 +1322,9 @@
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M43" s="2"/>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -1260,8 +1337,9 @@
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M44" s="2"/>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -1274,8 +1352,9 @@
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M45" s="2"/>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -1288,6 +1367,7 @@
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Shared/LoadedData.xlsx
+++ b/Shared/LoadedData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-29490" yWindow="2940" windowWidth="28800" windowHeight="15345" activeTab="1"/>
+    <workbookView xWindow="-32670" yWindow="3645" windowWidth="28800" windowHeight="15345" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="40">
   <si>
     <t>Description</t>
   </si>
@@ -1383,11 +1383,11 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col bestFit="true" customWidth="true" max="1" min="1" width="11.7109375"/>
-    <col bestFit="true" customWidth="true" max="2" min="2" width="7.42578125"/>
-    <col bestFit="true" customWidth="true" max="3" min="3" width="10.7109375"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" width="11.42578125"/>
+    <col bestFit="true" customWidth="true" max="3" min="3" width="18"/>
     <col bestFit="true" customWidth="true" max="4" min="4" width="7.5703125"/>
     <col bestFit="true" customWidth="true" max="5" min="5" width="3.42578125"/>
-    <col bestFit="true" customWidth="true" max="6" min="6" width="6.5703125"/>
+    <col bestFit="true" customWidth="true" max="6" min="6" width="7.5703125"/>
     <col bestFit="true" customWidth="true" max="7" min="7" width="7.28515625"/>
     <col bestFit="true" customWidth="true" max="8" min="8" width="2.85546875"/>
     <col bestFit="true" customWidth="true" max="11" min="11" width="11.42578125"/>
@@ -1460,6 +1460,9 @@
     <row r="5" spans="1:20" s="2" customFormat="true">
       <c r="A5" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>15</v>
